--- a/sample/予約状況_胃がん検診_サンプル.xlsx
+++ b/sample/予約状況_胃がん検診_サンプル.xlsx
@@ -416,9 +416,8 @@
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,14 +451,8 @@
       <c r="A2" t="n">
         <v>1001</v>
       </c>
-      <c r="B2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>総務部総務課</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>青木　一郎</t>
@@ -467,7 +460,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8/22　9：00〜9：20</t>
+          <t>【男】6日（火）　7：00〜7：15</t>
         </is>
       </c>
     </row>
@@ -475,14 +468,8 @@
       <c r="A3" t="n">
         <v>1002</v>
       </c>
-      <c r="B3" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>総務部総務課</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>石川　花</t>
@@ -490,7 +477,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8/22　9：20〜9：40</t>
+          <t>【女】6日（火）　7：15〜7：30</t>
         </is>
       </c>
     </row>
@@ -498,14 +485,8 @@
       <c r="A4" t="n">
         <v>1003</v>
       </c>
-      <c r="B4" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>総務部総務課</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>上田　次郎</t>
@@ -513,7 +494,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8/22　9：40〜10：00</t>
+          <t>【男】6日（火）　7：30〜7：45</t>
         </is>
       </c>
     </row>
@@ -521,14 +502,8 @@
       <c r="A5" t="n">
         <v>1004</v>
       </c>
-      <c r="B5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>総務部総務課</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>江口　美穂</t>
@@ -536,7 +511,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8/22　10：00〜10：20</t>
+          <t>【女】6日（火）　7：45〜8：00</t>
         </is>
       </c>
     </row>
@@ -544,14 +519,8 @@
       <c r="A6" t="n">
         <v>1101</v>
       </c>
-      <c r="B6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>総務部財政課</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>大野　三郎</t>
@@ -559,7 +528,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>派遣元自治体で受診</t>
+          <t>【男】6日（火）　8：00〜8：15</t>
         </is>
       </c>
     </row>
@@ -567,14 +536,8 @@
       <c r="A7" t="n">
         <v>1102</v>
       </c>
-      <c r="B7" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>総務部財政課</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>加藤　由紀</t>
@@ -582,7 +545,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8/22　10：20〜10：40</t>
+          <t>【女】6日（火）　8：15〜8：30</t>
         </is>
       </c>
     </row>
@@ -590,14 +553,8 @@
       <c r="A8" t="n">
         <v>1103</v>
       </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>総務部財政課</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>木下　健</t>
@@ -605,7 +562,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8/22　10：40〜11：00</t>
+          <t>派遣元自治体で受診</t>
         </is>
       </c>
     </row>
@@ -613,14 +570,8 @@
       <c r="A9" t="n">
         <v>1104</v>
       </c>
-      <c r="B9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>総務部財政課</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>熊谷　彩</t>
@@ -628,7 +579,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8/23　9：00〜9：20</t>
+          <t>【女】7日（水）　7：00〜7：15</t>
         </is>
       </c>
     </row>
@@ -636,14 +587,8 @@
       <c r="A10" t="n">
         <v>1201</v>
       </c>
-      <c r="B10" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>市民部市民課</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>小松　悟</t>
@@ -651,7 +596,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8/23　9：20〜9：40</t>
+          <t>【男】7日（水）　7：15〜7：30</t>
         </is>
       </c>
     </row>
@@ -659,37 +604,21 @@
       <c r="A11" t="n">
         <v>1202</v>
       </c>
-      <c r="B11" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>市民部市民課</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>佐藤　真理</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>派遣元で受診</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>1203</v>
       </c>
-      <c r="B12" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>市民部市民課</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>島田　浩</t>
@@ -697,7 +626,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8/23　9：40〜10：00</t>
+          <t>【男】7日（水）　7：30〜7：45</t>
         </is>
       </c>
     </row>
@@ -705,33 +634,25 @@
       <c r="A13" t="n">
         <v>1204</v>
       </c>
-      <c r="B13" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>市民部市民課</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>菅原　千尋</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>【女】7日（水）　7：45〜8：00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>1301</v>
       </c>
-      <c r="B14" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>市民部税務課</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>高橋　誠</t>
@@ -739,7 +660,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8/23　10：00〜10：20</t>
+          <t>【男】7日（水）　8：00〜8：15</t>
         </is>
       </c>
     </row>
@@ -747,14 +668,8 @@
       <c r="A15" t="n">
         <v>1302</v>
       </c>
-      <c r="B15" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>市民部税務課</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>千葉　結衣</t>
@@ -762,7 +677,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8/23　10：20〜10：40</t>
+          <t>他の受診機関で受診予定</t>
         </is>
       </c>
     </row>
@@ -770,14 +685,8 @@
       <c r="A16" t="n">
         <v>1303</v>
       </c>
-      <c r="B16" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>市民部税務課</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>角田　勇</t>
@@ -785,7 +694,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>他受診機関で受診</t>
+          <t>【男】7日（水）　8：15〜8：30</t>
         </is>
       </c>
     </row>
@@ -793,14 +702,8 @@
       <c r="A17" t="n">
         <v>1401</v>
       </c>
-      <c r="B17" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>保健福祉部健康推進課</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>照井　奈々</t>
@@ -808,7 +711,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8/23　10：40〜11：00</t>
+          <t>【女】8日（木）　7：00〜7：15</t>
         </is>
       </c>
     </row>
@@ -816,14 +719,8 @@
       <c r="A18" t="n">
         <v>1402</v>
       </c>
-      <c r="B18" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保健福祉部健康推進課</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>戸田　亮</t>
@@ -831,7 +728,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8/23　13：00〜13：20</t>
+          <t>【男】8日（木）　7：15〜7：30</t>
         </is>
       </c>
     </row>
@@ -839,14 +736,8 @@
       <c r="A19" t="n">
         <v>1403</v>
       </c>
-      <c r="B19" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保健福祉部健康推進課</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>中山　葵</t>
@@ -854,7 +745,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8/23　13：20〜13：40</t>
+          <t>【女】8日（木）　7：30〜7：45</t>
         </is>
       </c>
     </row>
@@ -862,14 +753,8 @@
       <c r="A20" t="n">
         <v>1404</v>
       </c>
-      <c r="B20" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保健福祉部健康推進課</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>沼田　武</t>
@@ -877,7 +762,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8/22　9：00〜9：20</t>
+          <t>【男】8日（木）　7：45〜8：00</t>
         </is>
       </c>
     </row>
@@ -885,14 +770,8 @@
       <c r="A21" t="n">
         <v>1501</v>
       </c>
-      <c r="B21" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>建設部建設課</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>野村　香</t>
@@ -900,7 +779,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>他の受診機関で受診予定</t>
+          <t>【女】8日（木）　8：00〜8：15</t>
         </is>
       </c>
     </row>
@@ -908,14 +787,8 @@
       <c r="A22" t="n">
         <v>1502</v>
       </c>
-      <c r="B22" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>建設部建設課</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>橋本　修一</t>
@@ -923,7 +796,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8/22　9：20〜9：40</t>
+          <t>受診しない</t>
         </is>
       </c>
     </row>
@@ -931,14 +804,8 @@
       <c r="A23" t="n">
         <v>1503</v>
       </c>
-      <c r="B23" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>建設部建設課</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>平野　さくら</t>
@@ -946,7 +813,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8/22　9：40〜10：00</t>
+          <t>【女】8日（木）　8：15〜8：30</t>
         </is>
       </c>
     </row>
@@ -954,14 +821,8 @@
       <c r="A24" t="n">
         <v>1601</v>
       </c>
-      <c r="B24" t="n">
-        <v>5100</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>議会事務局</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>福田　太一</t>
@@ -969,7 +830,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8/22　10：00〜10：20</t>
+          <t>【男】9日（金）　7：00〜7：15</t>
         </is>
       </c>
     </row>
@@ -977,14 +838,8 @@
       <c r="A25" t="n">
         <v>1602</v>
       </c>
-      <c r="B25" t="n">
-        <v>5100</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>議会事務局</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>星　美咲</t>
@@ -992,7 +847,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8/22　10：20〜10：40</t>
+          <t>【女】9日（金）　7：15〜7：30</t>
         </is>
       </c>
     </row>
